--- a/data/daily_visitor_status_sample_10.xlsx
+++ b/data/daily_visitor_status_sample_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,23 +27,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,14 +45,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -134,51 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Format: YYYY-MM-DD</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Must match an existing visitor profile.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Actual capacity for that day.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE/FALSE</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyVisitorStatus10Template" displayName="DailyVisitorStatus10Template" ref="A1:F11" headerRowCount="1">
-  <autoFilter ref="A1:F11"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="work_date"/>
-    <tableColumn id="2" name="visitor_code"/>
-    <tableColumn id="3" name="start_lat"/>
-    <tableColumn id="4" name="start_lon"/>
-    <tableColumn id="5" name="capacity"/>
-    <tableColumn id="6" name="is_active_today"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -470,16 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -489,25 +436,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>visitor_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>start_lat</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>start_lon</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>is_active_today</t>
         </is>
@@ -516,248 +473,344 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>visitor1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>VIS-001</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>35.777114</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.399439</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ویزیتور 01</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" t="b">
+        <v>35.67</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>visitor2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>VIS-002</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>35.745218</v>
-      </c>
-      <c r="D3" t="n">
-        <v>51.365308</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ویزیتور 02</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" t="b">
+        <v>35.68</v>
+      </c>
+      <c r="F3" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>visitor3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>VIS-003</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>35.711991</v>
-      </c>
-      <c r="D4" t="n">
-        <v>51.546789</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ویزیتور 03</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" t="b">
+        <v>35.69</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>visitor4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>VIS-004</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>35.743584</v>
-      </c>
-      <c r="D5" t="n">
-        <v>51.241966</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ویزیتور 04</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" t="b">
+        <v>35.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>visitor5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>VIS-005</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>35.660157</v>
-      </c>
-      <c r="D6" t="n">
-        <v>51.39285</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ویزیتور 05</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F6" t="b">
+        <v>35.71</v>
+      </c>
+      <c r="F6" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>visitor6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>VIS-006</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>35.780839</v>
-      </c>
-      <c r="D7" t="n">
-        <v>51.431808</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ویزیتور 06</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="b">
+        <v>35.72</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>visitor7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>VIS-007</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>35.715959</v>
-      </c>
-      <c r="D8" t="n">
-        <v>51.330832</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ویزیتور 07</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F8" t="b">
+        <v>35.73</v>
+      </c>
+      <c r="F8" t="n">
+        <v>51.39</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>visitor8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>VIS-008</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>35.741207</v>
-      </c>
-      <c r="D9" t="n">
-        <v>51.465581</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ویزیتور 08</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
-      </c>
-      <c r="F9" t="b">
+        <v>35.74</v>
+      </c>
+      <c r="F9" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>visitor9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>VIS-009</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>35.719552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>51.27121</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ویزیتور 09</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" t="b">
+        <v>35.75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>visitor10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>VIS-010</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>35.654035</v>
-      </c>
-      <c r="D11" t="n">
-        <v>51.360367</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ویزیتور 10</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
+        <v>35.76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data/daily_visitor_status_sample_10.xlsx
+++ b/data/daily_visitor_status_sample_10.xlsx
@@ -1,37 +1,162 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Arash\Python\bexlogix\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42440D4-EFC3-4FD7-AB9D-A9FD45A05667}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>work_date</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>visitor_code</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>start_lat</t>
+  </si>
+  <si>
+    <t>start_lon</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>is_active_today</t>
+  </si>
+  <si>
+    <t>visitor1</t>
+  </si>
+  <si>
+    <t>VIS-001</t>
+  </si>
+  <si>
+    <t>ویزیتور 01</t>
+  </si>
+  <si>
+    <t>visitor2</t>
+  </si>
+  <si>
+    <t>VIS-002</t>
+  </si>
+  <si>
+    <t>ویزیتور 02</t>
+  </si>
+  <si>
+    <t>visitor3</t>
+  </si>
+  <si>
+    <t>VIS-003</t>
+  </si>
+  <si>
+    <t>ویزیتور 03</t>
+  </si>
+  <si>
+    <t>visitor4</t>
+  </si>
+  <si>
+    <t>VIS-004</t>
+  </si>
+  <si>
+    <t>ویزیتور 04</t>
+  </si>
+  <si>
+    <t>visitor5</t>
+  </si>
+  <si>
+    <t>VIS-005</t>
+  </si>
+  <si>
+    <t>ویزیتور 05</t>
+  </si>
+  <si>
+    <t>visitor6</t>
+  </si>
+  <si>
+    <t>VIS-006</t>
+  </si>
+  <si>
+    <t>ویزیتور 06</t>
+  </si>
+  <si>
+    <t>visitor7</t>
+  </si>
+  <si>
+    <t>VIS-007</t>
+  </si>
+  <si>
+    <t>ویزیتور 07</t>
+  </si>
+  <si>
+    <t>visitor8</t>
+  </si>
+  <si>
+    <t>VIS-008</t>
+  </si>
+  <si>
+    <t>ویزیتور 08</t>
+  </si>
+  <si>
+    <t>visitor9</t>
+  </si>
+  <si>
+    <t>VIS-009</t>
+  </si>
+  <si>
+    <t>ویزیتور 09</t>
+  </si>
+  <si>
+    <t>visitor10</t>
+  </si>
+  <si>
+    <t>VIS-010</t>
+  </si>
+  <si>
+    <t>ویزیتور 10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +171,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,390 +496,293 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>work_date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>visitor_code</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>start_lat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>start_lon</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>is_active_today</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>visitor1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VIS-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ویزیتور 01</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2">
         <v>35.67</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>51.33</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>30</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>visitor2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VIS-002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ویزیتور 02</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
         <v>35.68</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>51.34</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>30</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>visitor3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VIS-003</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ویزیتور 03</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
         <v>35.69</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>51.35</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>30</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>visitor4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VIS-004</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ویزیتور 04</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="F5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="F5">
         <v>51.36</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>30</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>visitor5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VIS-005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ویزیتور 05</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
         <v>35.71</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>51.37</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>30</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>visitor6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VIS-006</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ویزیتور 06</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
         <v>35.72</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>51.38</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>30</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>visitor7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VIS-007</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ویزیتور 07</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="F8" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>35.729999999999997</v>
+      </c>
+      <c r="F8">
         <v>51.39</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>visitor8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VIS-008</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ویزیتور 08</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
         <v>35.74</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>51.4</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>30</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>visitor9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VIS-009</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ویزیتور 09</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10">
         <v>35.75</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>51.41</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>30</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>visitor10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VIS-010</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ویزیتور 10</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11">
         <v>35.76</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>51.42</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>30</v>
       </c>
       <c r="H11" t="b">
